--- a/feedback_forms/021_cybersecurity_awareness_survey_form--feedback_forms.xlsx
+++ b/feedback_forms/021_cybersecurity_awareness_survey_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>social_engineering</t>
+          <t>social engineering</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>in_person</t>
+          <t>in person</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>password_management</t>
+          <t>password management</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>data_protection</t>
+          <t>data protection</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>software_security</t>
+          <t>software security</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>password_management</t>
+          <t>password management</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>data_protection</t>
+          <t>data protection</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>software_security</t>
+          <t>software security</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>social_engineering</t>
+          <t>social engineering</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>software_security</t>
+          <t>software security</t>
         </is>
       </c>
     </row>
